--- a/docs/files/REPORT_FILTRI/Agente - CR FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR FELICI FILIPPO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -817,28 +817,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - CR FELICI FILIPPO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR FELICI FILIPPO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>4</v>
@@ -838,7 +838,7 @@
         <v>11</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
